--- a/artfynd/A 50776-2024 artfynd.xlsx
+++ b/artfynd/A 50776-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136437839</v>
       </c>
       <c r="B2" t="n">
-        <v>99377</v>
+        <v>99380</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50776-2024 artfynd.xlsx
+++ b/artfynd/A 50776-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136437839</v>
       </c>
       <c r="B2" t="n">
-        <v>99380</v>
+        <v>99381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50776-2024 artfynd.xlsx
+++ b/artfynd/A 50776-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136437839</v>
       </c>
       <c r="B2" t="n">
-        <v>99381</v>
+        <v>99386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50776-2024 artfynd.xlsx
+++ b/artfynd/A 50776-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136437839</v>
       </c>
       <c r="B2" t="n">
-        <v>99386</v>
+        <v>99388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50776-2024 artfynd.xlsx
+++ b/artfynd/A 50776-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136437839</v>
       </c>
       <c r="B2" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50776-2024 artfynd.xlsx
+++ b/artfynd/A 50776-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136437839</v>
       </c>
       <c r="B2" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50776-2024 artfynd.xlsx
+++ b/artfynd/A 50776-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Maria Magnusson, Emilia Fagerberg</t>
+          <t>Emilia Fagerberg, Maria Magnusson, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 50776-2024 artfynd.xlsx
+++ b/artfynd/A 50776-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136437839</v>
       </c>
       <c r="B2" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emilia Fagerberg, Maria Magnusson, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Maria Magnusson, Emilia Fagerberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
